--- a/Proyecto/output/indicadores_acceso_tecnologico.xlsx
+++ b/Proyecto/output/indicadores_acceso_tecnologico.xlsx
@@ -1,99 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10921"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulogarridogrijalva/Documents/GitHub/programa-II/Proyecto/output/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B1C887-0585-9141-BB5C-1E5E222FAEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="indicadores_basicos" sheetId="1" r:id="rId1"/>
     <sheet name="diccionario_variables" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
-  <si>
-    <t>depto</t>
-  </si>
-  <si>
-    <t>var_uso_cel</t>
-  </si>
-  <si>
-    <t>var_uso_intern</t>
-  </si>
-  <si>
-    <t>var_uso_intern_mujeres</t>
-  </si>
-  <si>
-    <t>var_uso_acceso_tel_mov</t>
-  </si>
-  <si>
-    <t>pct_rural</t>
-  </si>
-  <si>
-    <t>propor_hogares_internet</t>
-  </si>
-  <si>
-    <t>propor_hogares_computadora</t>
-  </si>
-  <si>
-    <t>pct_radiobases</t>
-  </si>
-  <si>
-    <t>pct_lineas_fijas</t>
-  </si>
-  <si>
-    <t>variable</t>
-  </si>
-  <si>
-    <t>descripcion</t>
-  </si>
-  <si>
-    <t>Departamento</t>
-  </si>
-  <si>
-    <t>Proporción de personas que usan teléfono celular por departamento</t>
-  </si>
-  <si>
-    <t>Proporción de personas que usan internet por departamento</t>
-  </si>
-  <si>
-    <t>Proporción de mujeres que usan internet por departamento</t>
-  </si>
-  <si>
-    <t>Proporción de personas con acceso a teléfono móvil por departamento</t>
-  </si>
-  <si>
-    <t>Porcentaje de población rural por departamento</t>
-  </si>
-  <si>
-    <t>Proporción de hogares con acceso a internet por departamento</t>
-  </si>
-  <si>
-    <t>Proporción de hogares con computadora por departamento</t>
-  </si>
-  <si>
-    <t>Proporción de radiobases por cada 1000 habitantes (línea móvil) por departamento</t>
-  </si>
-  <si>
-    <t>Proporción de líneas fijas por departamento</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,21 +64,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -193,7 +108,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -227,7 +142,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -262,10 +176,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -438,744 +351,764 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>depto</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>var_uso_intern</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>var_uso_intern_mujeres</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>var_uso_acceso_tel_mov</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>pct_rural</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>propor_hogares_internet</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>propor_hogares_computadora</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>rb_por_100k</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lineas_por_1k</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>73.849999999999994</v>
+        <v>56.4</v>
       </c>
       <c r="C2">
-        <v>56.4</v>
+        <v>30.73</v>
       </c>
       <c r="D2">
-        <v>30.73</v>
+        <v>69.2</v>
       </c>
       <c r="E2">
-        <v>69.2</v>
+        <v>10.24</v>
       </c>
       <c r="F2">
-        <v>10.24</v>
+        <v>36.88</v>
       </c>
       <c r="G2">
-        <v>36.880000000000003</v>
+        <v>36.67</v>
       </c>
       <c r="H2">
-        <v>36.67</v>
+        <v>167.7049777112282</v>
       </c>
       <c r="I2">
-        <v>31.28</v>
+        <v>404.8632795060066</v>
       </c>
       <c r="J2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>14654.86531187161</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>61.73</v>
+        <v>44.76</v>
       </c>
       <c r="C3">
-        <v>44.76</v>
+        <v>23.04</v>
       </c>
       <c r="D3">
-        <v>23.04</v>
+        <v>58.52</v>
       </c>
       <c r="E3">
-        <v>58.52</v>
+        <v>44.4</v>
       </c>
       <c r="F3">
-        <v>44.4</v>
+        <v>15.49</v>
       </c>
       <c r="G3">
-        <v>15.49</v>
+        <v>13.53</v>
       </c>
       <c r="H3">
-        <v>13.53</v>
+        <v>168.0911246870509</v>
       </c>
       <c r="I3">
-        <v>1.7</v>
+        <v>47.969449057217</v>
       </c>
       <c r="J3">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>5502.583359599408</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>68.87</v>
+        <v>47.32</v>
       </c>
       <c r="C4">
-        <v>47.32</v>
+        <v>22.53</v>
       </c>
       <c r="D4">
-        <v>22.53</v>
+        <v>66.05</v>
       </c>
       <c r="E4">
-        <v>66.05</v>
+        <v>12.8</v>
       </c>
       <c r="F4">
-        <v>12.8</v>
+        <v>15.62</v>
       </c>
       <c r="G4">
-        <v>15.62</v>
+        <v>29.89</v>
       </c>
       <c r="H4">
-        <v>29.89</v>
+        <v>133.1779590477776</v>
       </c>
       <c r="I4">
-        <v>2.79</v>
+        <v>54.60785945808322</v>
       </c>
       <c r="J4">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>6413.809557371761</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>58.85</v>
+        <v>36.8</v>
       </c>
       <c r="C5">
-        <v>36.799999999999997</v>
+        <v>18.81</v>
       </c>
       <c r="D5">
-        <v>18.809999999999999</v>
+        <v>55.73</v>
       </c>
       <c r="E5">
-        <v>55.73</v>
+        <v>50.26</v>
       </c>
       <c r="F5">
-        <v>50.26</v>
+        <v>17.28</v>
       </c>
       <c r="G5">
-        <v>17.28</v>
+        <v>14.9</v>
       </c>
       <c r="H5">
-        <v>14.9</v>
+        <v>75.27008486993563</v>
       </c>
       <c r="I5">
-        <v>2.98</v>
+        <v>18.812339111813</v>
       </c>
       <c r="J5">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2841.710966594324</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>64.8</v>
+        <v>47.95</v>
       </c>
       <c r="C6">
-        <v>47.95</v>
+        <v>25.4</v>
       </c>
       <c r="D6">
-        <v>25.4</v>
+        <v>59.28</v>
       </c>
       <c r="E6">
-        <v>59.28</v>
+        <v>42.99</v>
       </c>
       <c r="F6">
-        <v>42.99</v>
+        <v>16.35</v>
       </c>
       <c r="G6">
-        <v>16.350000000000001</v>
+        <v>11.85</v>
       </c>
       <c r="H6">
-        <v>11.85</v>
+        <v>130.9968385934412</v>
       </c>
       <c r="I6">
-        <v>5.53</v>
+        <v>30.04307477139291</v>
       </c>
       <c r="J6">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10861.05517605828</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>62.88</v>
+        <v>44.69</v>
       </c>
       <c r="C7">
-        <v>44.69</v>
+        <v>21.98</v>
       </c>
       <c r="D7">
-        <v>21.98</v>
+        <v>58.33</v>
       </c>
       <c r="E7">
-        <v>58.33</v>
+        <v>54.36</v>
       </c>
       <c r="F7">
-        <v>54.36</v>
+        <v>17.95</v>
       </c>
       <c r="G7">
-        <v>17.95</v>
+        <v>6.91</v>
       </c>
       <c r="H7">
-        <v>6.91</v>
+        <v>133.5002451152041</v>
       </c>
       <c r="I7">
-        <v>3.13</v>
+        <v>21.56794943623503</v>
       </c>
       <c r="J7">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>4447.281194428339</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>55.61</v>
+        <v>35.84</v>
       </c>
       <c r="C8">
-        <v>35.840000000000003</v>
+        <v>17.82</v>
       </c>
       <c r="D8">
-        <v>17.82</v>
+        <v>53.3</v>
       </c>
       <c r="E8">
-        <v>53.3</v>
+        <v>35.3</v>
       </c>
       <c r="F8">
-        <v>35.299999999999997</v>
+        <v>21.05</v>
       </c>
       <c r="G8">
-        <v>21.05</v>
+        <v>17.03</v>
       </c>
       <c r="H8">
-        <v>17.03</v>
+        <v>78.08881218923317</v>
       </c>
       <c r="I8">
-        <v>1.95</v>
+        <v>20.3051407443237</v>
       </c>
       <c r="J8">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>3253.97911654683</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>51.39</v>
+        <v>32.52</v>
       </c>
       <c r="C9">
-        <v>32.520000000000003</v>
+        <v>16.31</v>
       </c>
       <c r="D9">
-        <v>16.309999999999999</v>
+        <v>48.51</v>
       </c>
       <c r="E9">
-        <v>48.51</v>
+        <v>50.41</v>
       </c>
       <c r="F9">
-        <v>50.41</v>
+        <v>17.02</v>
       </c>
       <c r="G9">
-        <v>17.02</v>
+        <v>13.58</v>
       </c>
       <c r="H9">
-        <v>13.58</v>
+        <v>67.33542690069993</v>
       </c>
       <c r="I9">
-        <v>1.75</v>
+        <v>24.89245035981138</v>
       </c>
       <c r="J9">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>3705.363402438045</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>61.85</v>
+        <v>44.65</v>
       </c>
       <c r="C10">
-        <v>44.65</v>
+        <v>23.89</v>
       </c>
       <c r="D10">
-        <v>23.89</v>
+        <v>58.31</v>
       </c>
       <c r="E10">
-        <v>58.31</v>
+        <v>43.76</v>
       </c>
       <c r="F10">
-        <v>43.76</v>
+        <v>25.74</v>
       </c>
       <c r="G10">
-        <v>25.74</v>
+        <v>19.77</v>
       </c>
       <c r="H10">
-        <v>19.77</v>
+        <v>116.4051111455224</v>
       </c>
       <c r="I10">
-        <v>5.58</v>
+        <v>154.4247291445292</v>
       </c>
       <c r="J10">
-        <v>7.46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>7089.645961795169</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>55.43</v>
+        <v>39.05</v>
       </c>
       <c r="C11">
-        <v>39.049999999999997</v>
+        <v>19.04</v>
       </c>
       <c r="D11">
-        <v>19.04</v>
+        <v>52.36</v>
       </c>
       <c r="E11">
-        <v>52.36</v>
+        <v>50.69</v>
       </c>
       <c r="F11">
-        <v>50.69</v>
+        <v>12.35</v>
       </c>
       <c r="G11">
-        <v>12.35</v>
+        <v>10.19</v>
       </c>
       <c r="H11">
-        <v>10.19</v>
+        <v>103.7644132760979</v>
       </c>
       <c r="I11">
-        <v>3.33</v>
+        <v>23.16340979440279</v>
       </c>
       <c r="J11">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>4277.287592846576</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>59.49</v>
+        <v>38.98</v>
       </c>
       <c r="C12">
-        <v>38.979999999999997</v>
+        <v>19.53</v>
       </c>
       <c r="D12">
-        <v>19.53</v>
+        <v>55.3</v>
       </c>
       <c r="E12">
-        <v>55.3</v>
+        <v>47.41</v>
       </c>
       <c r="F12">
-        <v>47.41</v>
+        <v>13.36</v>
       </c>
       <c r="G12">
-        <v>13.36</v>
+        <v>10.97</v>
       </c>
       <c r="H12">
-        <v>10.97</v>
+        <v>117.3784783715934</v>
       </c>
       <c r="I12">
-        <v>2.33</v>
+        <v>27.74165358870478</v>
       </c>
       <c r="J12">
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>5334.328928231918</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>53.99</v>
+        <v>36.12</v>
       </c>
       <c r="C13">
-        <v>36.119999999999997</v>
+        <v>19.69</v>
       </c>
       <c r="D13">
-        <v>19.690000000000001</v>
+        <v>50.81</v>
       </c>
       <c r="E13">
-        <v>50.81</v>
+        <v>75.36</v>
       </c>
       <c r="F13">
-        <v>75.36</v>
+        <v>11.71</v>
       </c>
       <c r="G13">
-        <v>11.71</v>
+        <v>10.95</v>
       </c>
       <c r="H13">
-        <v>10.95</v>
+        <v>80.70642241594307</v>
       </c>
       <c r="I13">
-        <v>5.0599999999999996</v>
+        <v>17.04238354602924</v>
       </c>
       <c r="J13">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>4681.389763386482</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>51.83</v>
+        <v>32.69</v>
       </c>
       <c r="C14">
-        <v>32.69</v>
+        <v>17.39</v>
       </c>
       <c r="D14">
-        <v>17.39</v>
+        <v>49.35</v>
       </c>
       <c r="E14">
-        <v>49.35</v>
+        <v>64.52</v>
       </c>
       <c r="F14">
-        <v>64.52</v>
+        <v>15.5</v>
       </c>
       <c r="G14">
-        <v>15.5</v>
+        <v>12.22</v>
       </c>
       <c r="H14">
-        <v>12.22</v>
+        <v>81.84212173293471</v>
       </c>
       <c r="I14">
-        <v>6.1</v>
+        <v>16.08575953959336</v>
       </c>
       <c r="J14">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2860.377541927725</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>48.67</v>
+        <v>27.64</v>
       </c>
       <c r="C15">
-        <v>27.64</v>
+        <v>14.43</v>
       </c>
       <c r="D15">
-        <v>14.43</v>
+        <v>46.65</v>
       </c>
       <c r="E15">
-        <v>46.65</v>
+        <v>63.33</v>
       </c>
       <c r="F15">
-        <v>63.33</v>
+        <v>8.48</v>
       </c>
       <c r="G15">
-        <v>8.48</v>
+        <v>8.49</v>
       </c>
       <c r="H15">
-        <v>8.49</v>
+        <v>67.71333497107889</v>
       </c>
       <c r="I15">
-        <v>3.88</v>
+        <v>8.373941979141076</v>
       </c>
       <c r="J15">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2601.343610276273</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>53.31</v>
+        <v>29.8</v>
       </c>
       <c r="C16">
-        <v>29.8</v>
+        <v>16.08</v>
       </c>
       <c r="D16">
-        <v>16.079999999999998</v>
+        <v>50.71</v>
       </c>
       <c r="E16">
-        <v>50.71</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="F16">
-        <v>65.260000000000005</v>
+        <v>10.07</v>
       </c>
       <c r="G16">
-        <v>10.07</v>
+        <v>14.64</v>
       </c>
       <c r="H16">
-        <v>14.64</v>
+        <v>88.49429139284213</v>
       </c>
       <c r="I16">
-        <v>1.56</v>
+        <v>14.32446939693316</v>
       </c>
       <c r="J16">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2997.228256804486</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>41.22</v>
+        <v>21.62</v>
       </c>
       <c r="C17">
-        <v>21.62</v>
+        <v>9.25</v>
       </c>
       <c r="D17">
-        <v>9.25</v>
+        <v>37.58</v>
       </c>
       <c r="E17">
-        <v>37.58</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="F17">
-        <v>69.790000000000006</v>
+        <v>6.14</v>
       </c>
       <c r="G17">
-        <v>6.14</v>
+        <v>7.36</v>
       </c>
       <c r="H17">
-        <v>7.36</v>
+        <v>51.95359002149926</v>
       </c>
       <c r="I17">
-        <v>3.75</v>
+        <v>8.938007498089942</v>
       </c>
       <c r="J17">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>3424.98228253698</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>56.74</v>
+        <v>42.63</v>
       </c>
       <c r="C18">
-        <v>42.63</v>
+        <v>22.49</v>
       </c>
       <c r="D18">
-        <v>22.49</v>
+        <v>52.29</v>
       </c>
       <c r="E18">
-        <v>52.29</v>
+        <v>63.06</v>
       </c>
       <c r="F18">
-        <v>63.06</v>
+        <v>16.35</v>
       </c>
       <c r="G18">
-        <v>16.350000000000001</v>
+        <v>13.88</v>
       </c>
       <c r="H18">
-        <v>13.88</v>
+        <v>127.782351351478</v>
       </c>
       <c r="I18">
-        <v>4.1900000000000004</v>
+        <v>18.94709217044104</v>
       </c>
       <c r="J18">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+        <v>5385.839495294834</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>56.4</v>
+        <v>41.53</v>
       </c>
       <c r="C19">
-        <v>41.53</v>
+        <v>21.34</v>
       </c>
       <c r="D19">
-        <v>21.34</v>
+        <v>51.11</v>
       </c>
       <c r="E19">
-        <v>51.11</v>
+        <v>63.21</v>
       </c>
       <c r="F19">
-        <v>63.21</v>
+        <v>24.37</v>
       </c>
       <c r="G19">
-        <v>24.37</v>
+        <v>11.15</v>
       </c>
       <c r="H19">
-        <v>11.15</v>
+        <v>134.6846915676905</v>
       </c>
       <c r="I19">
-        <v>3.16</v>
+        <v>45.01568410873443</v>
       </c>
       <c r="J19">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+        <v>6539.42255530219</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>57.78</v>
+        <v>41.67</v>
       </c>
       <c r="C20">
-        <v>41.67</v>
+        <v>21.28</v>
       </c>
       <c r="D20">
-        <v>21.28</v>
+        <v>55.41</v>
       </c>
       <c r="E20">
-        <v>55.41</v>
+        <v>57.12</v>
       </c>
       <c r="F20">
-        <v>57.12</v>
+        <v>19.76</v>
       </c>
       <c r="G20">
-        <v>19.760000000000002</v>
+        <v>14.71</v>
       </c>
       <c r="H20">
-        <v>14.71</v>
+        <v>127.5764461986206</v>
       </c>
       <c r="I20">
-        <v>1.8</v>
+        <v>49.98677119236861</v>
       </c>
       <c r="J20">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+        <v>7132.596976437169</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>52.25</v>
+        <v>34.24</v>
       </c>
       <c r="C21">
-        <v>34.24</v>
+        <v>17.23</v>
       </c>
       <c r="D21">
-        <v>17.23</v>
+        <v>50.4</v>
       </c>
       <c r="E21">
-        <v>50.4</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="F21">
-        <v>64.180000000000007</v>
+        <v>24.74</v>
       </c>
       <c r="G21">
-        <v>24.74</v>
+        <v>11.23</v>
       </c>
       <c r="H21">
-        <v>11.23</v>
+        <v>106.2500272156832</v>
       </c>
       <c r="I21">
-        <v>2.5</v>
+        <v>27.65984315057458</v>
       </c>
       <c r="J21">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+        <v>4013.823897359814</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>52.17</v>
+        <v>32.76</v>
       </c>
       <c r="C22">
-        <v>32.76</v>
+        <v>19.16</v>
       </c>
       <c r="D22">
-        <v>19.16</v>
+        <v>49.28</v>
       </c>
       <c r="E22">
-        <v>49.28</v>
+        <v>42.43</v>
       </c>
       <c r="F22">
-        <v>42.43</v>
+        <v>20.31</v>
       </c>
       <c r="G22">
-        <v>20.309999999999999</v>
+        <v>12.89</v>
       </c>
       <c r="H22">
-        <v>12.89</v>
+        <v>94.2215607922342</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>21.79175585502443</v>
       </c>
       <c r="J22">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+        <v>3297.504029218479</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>64.17</v>
+        <v>44.26</v>
       </c>
       <c r="C23">
-        <v>44.26</v>
+        <v>23.97</v>
       </c>
       <c r="D23">
-        <v>23.97</v>
+        <v>60.09</v>
       </c>
       <c r="E23">
-        <v>60.09</v>
+        <v>52.28</v>
       </c>
       <c r="F23">
-        <v>52.28</v>
+        <v>21.69</v>
       </c>
       <c r="G23">
-        <v>21.69</v>
+        <v>9.56</v>
       </c>
       <c r="H23">
-        <v>9.56</v>
+        <v>126.782490894712</v>
       </c>
       <c r="I23">
-        <v>3.66</v>
+        <v>93.56370509860663</v>
       </c>
       <c r="J23">
-        <v>2.72</v>
+        <v>3875.954919188006</v>
       </c>
     </row>
   </sheetData>
@@ -1184,100 +1117,140 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>depto</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>var_uso_intern</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Proporción de personas que usan internet por departamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>var_uso_intern_mujeres</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Proporción de mujeres que usan internet por departamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>var_uso_acceso_tel_mov</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Proporción de personas con acceso a teléfono móvil por departamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>pct_rural</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Porcentaje de población rural por departamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>propor_hogares_internet</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Proporción de hogares con acceso a internet por departamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>propor_hogares_computadora</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Proporción de hogares con computadora por departamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rb_por_100k</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Radiobases por cada 100k habitantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lineas_por_1k</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Líneas fijas por cada 1k habitantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pib percapita</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PIB per capita</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Proyecto/output/indicadores_acceso_tecnologico.xlsx
+++ b/Proyecto/output/indicadores_acceso_tecnologico.xlsx
@@ -430,10 +430,10 @@
         <v>36.67</v>
       </c>
       <c r="H2">
-        <v>167.7049777112282</v>
+        <v>167.7</v>
       </c>
       <c r="I2">
-        <v>404.8632795060066</v>
+        <v>404.86</v>
       </c>
       <c r="J2">
         <v>14654.86531187161</v>
@@ -462,10 +462,10 @@
         <v>13.53</v>
       </c>
       <c r="H3">
-        <v>168.0911246870509</v>
+        <v>168.09</v>
       </c>
       <c r="I3">
-        <v>47.969449057217</v>
+        <v>47.97</v>
       </c>
       <c r="J3">
         <v>5502.583359599408</v>
@@ -494,10 +494,10 @@
         <v>29.89</v>
       </c>
       <c r="H4">
-        <v>133.1779590477776</v>
+        <v>133.18</v>
       </c>
       <c r="I4">
-        <v>54.60785945808322</v>
+        <v>54.61</v>
       </c>
       <c r="J4">
         <v>6413.809557371761</v>
@@ -526,10 +526,10 @@
         <v>14.9</v>
       </c>
       <c r="H5">
-        <v>75.27008486993563</v>
+        <v>75.27</v>
       </c>
       <c r="I5">
-        <v>18.812339111813</v>
+        <v>18.81</v>
       </c>
       <c r="J5">
         <v>2841.710966594324</v>
@@ -558,10 +558,10 @@
         <v>11.85</v>
       </c>
       <c r="H6">
-        <v>130.9968385934412</v>
+        <v>131</v>
       </c>
       <c r="I6">
-        <v>30.04307477139291</v>
+        <v>30.04</v>
       </c>
       <c r="J6">
         <v>10861.05517605828</v>
@@ -590,10 +590,10 @@
         <v>6.91</v>
       </c>
       <c r="H7">
-        <v>133.5002451152041</v>
+        <v>133.5</v>
       </c>
       <c r="I7">
-        <v>21.56794943623503</v>
+        <v>21.57</v>
       </c>
       <c r="J7">
         <v>4447.281194428339</v>
@@ -622,10 +622,10 @@
         <v>17.03</v>
       </c>
       <c r="H8">
-        <v>78.08881218923317</v>
+        <v>78.09</v>
       </c>
       <c r="I8">
-        <v>20.3051407443237</v>
+        <v>20.31</v>
       </c>
       <c r="J8">
         <v>3253.97911654683</v>
@@ -654,10 +654,10 @@
         <v>13.58</v>
       </c>
       <c r="H9">
-        <v>67.33542690069993</v>
+        <v>67.34</v>
       </c>
       <c r="I9">
-        <v>24.89245035981138</v>
+        <v>24.89</v>
       </c>
       <c r="J9">
         <v>3705.363402438045</v>
@@ -686,10 +686,10 @@
         <v>19.77</v>
       </c>
       <c r="H10">
-        <v>116.4051111455224</v>
+        <v>116.41</v>
       </c>
       <c r="I10">
-        <v>154.4247291445292</v>
+        <v>154.42</v>
       </c>
       <c r="J10">
         <v>7089.645961795169</v>
@@ -718,10 +718,10 @@
         <v>10.19</v>
       </c>
       <c r="H11">
-        <v>103.7644132760979</v>
+        <v>103.76</v>
       </c>
       <c r="I11">
-        <v>23.16340979440279</v>
+        <v>23.16</v>
       </c>
       <c r="J11">
         <v>4277.287592846576</v>
@@ -750,10 +750,10 @@
         <v>10.97</v>
       </c>
       <c r="H12">
-        <v>117.3784783715934</v>
+        <v>117.38</v>
       </c>
       <c r="I12">
-        <v>27.74165358870478</v>
+        <v>27.74</v>
       </c>
       <c r="J12">
         <v>5334.328928231918</v>
@@ -782,10 +782,10 @@
         <v>10.95</v>
       </c>
       <c r="H13">
-        <v>80.70642241594307</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="I13">
-        <v>17.04238354602924</v>
+        <v>17.04</v>
       </c>
       <c r="J13">
         <v>4681.389763386482</v>
@@ -814,10 +814,10 @@
         <v>12.22</v>
       </c>
       <c r="H14">
-        <v>81.84212173293471</v>
+        <v>81.84</v>
       </c>
       <c r="I14">
-        <v>16.08575953959336</v>
+        <v>16.09</v>
       </c>
       <c r="J14">
         <v>2860.377541927725</v>
@@ -846,10 +846,10 @@
         <v>8.49</v>
       </c>
       <c r="H15">
-        <v>67.71333497107889</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="I15">
-        <v>8.373941979141076</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="J15">
         <v>2601.343610276273</v>
@@ -878,10 +878,10 @@
         <v>14.64</v>
       </c>
       <c r="H16">
-        <v>88.49429139284213</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="I16">
-        <v>14.32446939693316</v>
+        <v>14.32</v>
       </c>
       <c r="J16">
         <v>2997.228256804486</v>
@@ -910,10 +910,10 @@
         <v>7.36</v>
       </c>
       <c r="H17">
-        <v>51.95359002149926</v>
+        <v>51.95</v>
       </c>
       <c r="I17">
-        <v>8.938007498089942</v>
+        <v>8.94</v>
       </c>
       <c r="J17">
         <v>3424.98228253698</v>
@@ -942,10 +942,10 @@
         <v>13.88</v>
       </c>
       <c r="H18">
-        <v>127.782351351478</v>
+        <v>127.78</v>
       </c>
       <c r="I18">
-        <v>18.94709217044104</v>
+        <v>18.95</v>
       </c>
       <c r="J18">
         <v>5385.839495294834</v>
@@ -974,10 +974,10 @@
         <v>11.15</v>
       </c>
       <c r="H19">
-        <v>134.6846915676905</v>
+        <v>134.68</v>
       </c>
       <c r="I19">
-        <v>45.01568410873443</v>
+        <v>45.02</v>
       </c>
       <c r="J19">
         <v>6539.42255530219</v>
@@ -1006,10 +1006,10 @@
         <v>14.71</v>
       </c>
       <c r="H20">
-        <v>127.5764461986206</v>
+        <v>127.58</v>
       </c>
       <c r="I20">
-        <v>49.98677119236861</v>
+        <v>49.99</v>
       </c>
       <c r="J20">
         <v>7132.596976437169</v>
@@ -1038,10 +1038,10 @@
         <v>11.23</v>
       </c>
       <c r="H21">
-        <v>106.2500272156832</v>
+        <v>106.25</v>
       </c>
       <c r="I21">
-        <v>27.65984315057458</v>
+        <v>27.66</v>
       </c>
       <c r="J21">
         <v>4013.823897359814</v>
@@ -1070,10 +1070,10 @@
         <v>12.89</v>
       </c>
       <c r="H22">
-        <v>94.2215607922342</v>
+        <v>94.22</v>
       </c>
       <c r="I22">
-        <v>21.79175585502443</v>
+        <v>21.79</v>
       </c>
       <c r="J22">
         <v>3297.504029218479</v>
@@ -1102,10 +1102,10 @@
         <v>9.56</v>
       </c>
       <c r="H23">
-        <v>126.782490894712</v>
+        <v>126.78</v>
       </c>
       <c r="I23">
-        <v>93.56370509860663</v>
+        <v>93.56</v>
       </c>
       <c r="J23">
         <v>3875.954919188006</v>
@@ -1244,7 +1244,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pib percapita</t>
+          <t>pib_per_capita</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">

--- a/Proyecto/output/indicadores_acceso_tecnologico.xlsx
+++ b/Proyecto/output/indicadores_acceso_tecnologico.xlsx
@@ -1,22 +1,102 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/D11B7E7C31B62C39/Escritorio/PROGRAMACIÓN II/programa-II/Proyecto/output/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_3E5C4BAEF1248DD158C55A7E6BBD231897459A04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9610A05-B883-4287-BFC7-7C130EBAF257}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indicadores_basicos" sheetId="1" r:id="rId1"/>
     <sheet name="diccionario_variables" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+  <si>
+    <t>depto</t>
+  </si>
+  <si>
+    <t>var_uso_intern</t>
+  </si>
+  <si>
+    <t>var_uso_intern_mujeres</t>
+  </si>
+  <si>
+    <t>var_uso_acceso_tel_mov</t>
+  </si>
+  <si>
+    <t>pct_rural</t>
+  </si>
+  <si>
+    <t>propor_hogares_internet</t>
+  </si>
+  <si>
+    <t>propor_hogares_computadora</t>
+  </si>
+  <si>
+    <t>rb_por_100k</t>
+  </si>
+  <si>
+    <t>lineas_por_1k</t>
+  </si>
+  <si>
+    <t>pib_per_capita</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>descripcion</t>
+  </si>
+  <si>
+    <t>Departamento</t>
+  </si>
+  <si>
+    <t>Proporción de personas que usan internet por departamento</t>
+  </si>
+  <si>
+    <t>Proporción de mujeres que usan internet por departamento</t>
+  </si>
+  <si>
+    <t>Proporción de personas con acceso a teléfono móvil por departamento</t>
+  </si>
+  <si>
+    <t>Porcentaje de población rural por departamento</t>
+  </si>
+  <si>
+    <t>Proporción de hogares con acceso a internet por departamento</t>
+  </si>
+  <si>
+    <t>Proporción de hogares con computadora por departamento</t>
+  </si>
+  <si>
+    <t>Radiobases por cada 100k habitantes</t>
+  </si>
+  <si>
+    <t>Líneas fijas por cada 1k habitantes</t>
+  </si>
+  <si>
+    <t>PIB per capita</t>
+  </si>
+  <si>
+    <t>IDTR</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,13 +144,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -108,7 +196,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -142,6 +230,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -176,9 +265,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -351,63 +441,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>depto</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>var_uso_intern</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>var_uso_intern_mujeres</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>var_uso_acceso_tel_mov</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>pct_rural</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>propor_hogares_internet</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>propor_hogares_computadora</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>rb_por_100k</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>lineas_por_1k</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>pib_per_capita</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -424,7 +497,7 @@
         <v>10.24</v>
       </c>
       <c r="F2">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="G2">
         <v>36.67</v>
@@ -438,8 +511,11 @@
       <c r="J2">
         <v>14654.86531187161</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="K2">
+        <v>77.576314310000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -468,10 +544,13 @@
         <v>47.97</v>
       </c>
       <c r="J3">
-        <v>5502.583359599408</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>5502.5833595994081</v>
+      </c>
+      <c r="K3">
+        <v>43.468735770000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -502,16 +581,19 @@
       <c r="J4">
         <v>6413.809557371761</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="K4">
+        <v>56.074692450000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>36.8</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="C5">
-        <v>18.81</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="D5">
         <v>55.73</v>
@@ -529,13 +611,16 @@
         <v>75.27</v>
       </c>
       <c r="I5">
-        <v>18.81</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="J5">
         <v>2841.710966594324</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="K5">
+        <v>36.326530650000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -552,7 +637,7 @@
         <v>42.99</v>
       </c>
       <c r="F6">
-        <v>16.35</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="G6">
         <v>11.85</v>
@@ -566,8 +651,11 @@
       <c r="J6">
         <v>10861.05517605828</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="K6">
+        <v>48.678756980000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -596,15 +684,18 @@
         <v>21.57</v>
       </c>
       <c r="J7">
-        <v>4447.281194428339</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>4447.2811944283394</v>
+      </c>
+      <c r="K7">
+        <v>38.768372200000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>35.84</v>
+        <v>35.840000000000003</v>
       </c>
       <c r="C8">
         <v>17.82</v>
@@ -613,7 +704,7 @@
         <v>53.3</v>
       </c>
       <c r="E8">
-        <v>35.3</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="F8">
         <v>21.05</v>
@@ -625,21 +716,24 @@
         <v>78.09</v>
       </c>
       <c r="I8">
-        <v>20.31</v>
+        <v>20.309999999999999</v>
       </c>
       <c r="J8">
         <v>3253.97911654683</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="K8">
+        <v>41.421687470000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>32.52</v>
+        <v>32.520000000000003</v>
       </c>
       <c r="C9">
-        <v>16.31</v>
+        <v>16.309999999999999</v>
       </c>
       <c r="D9">
         <v>48.51</v>
@@ -660,10 +754,13 @@
         <v>24.89</v>
       </c>
       <c r="J9">
-        <v>3705.363402438045</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>3705.3634024380449</v>
+      </c>
+      <c r="K9">
+        <v>32.234150679999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -689,18 +786,21 @@
         <v>116.41</v>
       </c>
       <c r="I10">
-        <v>154.42</v>
+        <v>154.41999999999999</v>
       </c>
       <c r="J10">
-        <v>7089.645961795169</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>7089.6459617951687</v>
+      </c>
+      <c r="K10">
+        <v>50.2077958</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>39.05</v>
+        <v>39.049999999999997</v>
       </c>
       <c r="C11">
         <v>19.04</v>
@@ -724,15 +824,18 @@
         <v>23.16</v>
       </c>
       <c r="J11">
-        <v>4277.287592846576</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>4277.2875928465764</v>
+      </c>
+      <c r="K11">
+        <v>36.171659529999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>38.98</v>
+        <v>38.979999999999997</v>
       </c>
       <c r="C12">
         <v>19.53</v>
@@ -756,18 +859,21 @@
         <v>27.74</v>
       </c>
       <c r="J12">
-        <v>5334.328928231918</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>5334.3289282319183</v>
+      </c>
+      <c r="K12">
+        <v>38.647416249999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>36.12</v>
+        <v>36.119999999999997</v>
       </c>
       <c r="C13">
-        <v>19.69</v>
+        <v>19.690000000000001</v>
       </c>
       <c r="D13">
         <v>50.81</v>
@@ -782,16 +888,19 @@
         <v>10.95</v>
       </c>
       <c r="H13">
-        <v>80.70999999999999</v>
+        <v>80.709999999999994</v>
       </c>
       <c r="I13">
         <v>17.04</v>
       </c>
       <c r="J13">
-        <v>4681.389763386482</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>4681.3897633864817</v>
+      </c>
+      <c r="K13">
+        <v>29.827691529999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -820,10 +929,13 @@
         <v>16.09</v>
       </c>
       <c r="J14">
-        <v>2860.377541927725</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>2860.3775419277249</v>
+      </c>
+      <c r="K14">
+        <v>30.658266730000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -846,16 +958,19 @@
         <v>8.49</v>
       </c>
       <c r="H15">
-        <v>67.70999999999999</v>
+        <v>67.709999999999994</v>
       </c>
       <c r="I15">
-        <v>8.369999999999999</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="J15">
         <v>2601.343610276273</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="K15">
+        <v>23.099284000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -863,13 +978,13 @@
         <v>29.8</v>
       </c>
       <c r="C16">
-        <v>16.08</v>
+        <v>16.079999999999998</v>
       </c>
       <c r="D16">
         <v>50.71</v>
       </c>
       <c r="E16">
-        <v>65.26000000000001</v>
+        <v>65.260000000000005</v>
       </c>
       <c r="F16">
         <v>10.07</v>
@@ -878,16 +993,19 @@
         <v>14.64</v>
       </c>
       <c r="H16">
-        <v>88.48999999999999</v>
+        <v>88.49</v>
       </c>
       <c r="I16">
         <v>14.32</v>
       </c>
       <c r="J16">
-        <v>2997.228256804486</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>2997.2282568044861</v>
+      </c>
+      <c r="K16">
+        <v>29.059082320000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -901,7 +1019,7 @@
         <v>37.58</v>
       </c>
       <c r="E17">
-        <v>69.79000000000001</v>
+        <v>69.790000000000006</v>
       </c>
       <c r="F17">
         <v>6.14</v>
@@ -916,10 +1034,13 @@
         <v>8.94</v>
       </c>
       <c r="J17">
-        <v>3424.98228253698</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>3424.9822825369802</v>
+      </c>
+      <c r="K17">
+        <v>14.070769609999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -936,7 +1057,7 @@
         <v>63.06</v>
       </c>
       <c r="F18">
-        <v>16.35</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="G18">
         <v>13.88</v>
@@ -948,10 +1069,13 @@
         <v>18.95</v>
       </c>
       <c r="J18">
-        <v>5385.839495294834</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>5385.8394952948338</v>
+      </c>
+      <c r="K18">
+        <v>37.506132200000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -980,10 +1104,13 @@
         <v>45.02</v>
       </c>
       <c r="J19">
-        <v>6539.42255530219</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>6539.4225553021897</v>
+      </c>
+      <c r="K19">
+        <v>39.219556609999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1000,7 +1127,7 @@
         <v>57.12</v>
       </c>
       <c r="F20">
-        <v>19.76</v>
+        <v>19.760000000000002</v>
       </c>
       <c r="G20">
         <v>14.71</v>
@@ -1012,10 +1139,13 @@
         <v>49.99</v>
       </c>
       <c r="J20">
-        <v>7132.596976437169</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>7132.5969764371694</v>
+      </c>
+      <c r="K20">
+        <v>41.535291579999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1029,7 +1159,7 @@
         <v>50.4</v>
       </c>
       <c r="E21">
-        <v>64.18000000000001</v>
+        <v>64.180000000000007</v>
       </c>
       <c r="F21">
         <v>24.74</v>
@@ -1044,10 +1174,13 @@
         <v>27.66</v>
       </c>
       <c r="J21">
-        <v>4013.823897359814</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>4013.8238973598141</v>
+      </c>
+      <c r="K21">
+        <v>34.229939829999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1064,7 +1197,7 @@
         <v>42.43</v>
       </c>
       <c r="F22">
-        <v>20.31</v>
+        <v>20.309999999999999</v>
       </c>
       <c r="G22">
         <v>12.89</v>
@@ -1078,8 +1211,11 @@
       <c r="J22">
         <v>3297.504029218479</v>
       </c>
-    </row>
-    <row r="23">
+      <c r="K22">
+        <v>37.707302460000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1109,6 +1245,9 @@
       </c>
       <c r="J23">
         <v>3875.954919188006</v>
+      </c>
+      <c r="K23">
+        <v>41.69458479</v>
       </c>
     </row>
   </sheetData>
@@ -1117,140 +1256,96 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>descripcion</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>depto</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>var_uso_intern</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Proporción de personas que usan internet por departamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>var_uso_intern_mujeres</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Proporción de mujeres que usan internet por departamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>var_uso_acceso_tel_mov</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Proporción de personas con acceso a teléfono móvil por departamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>pct_rural</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Porcentaje de población rural por departamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>propor_hogares_internet</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Proporción de hogares con acceso a internet por departamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>propor_hogares_computadora</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Proporción de hogares con computadora por departamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>rb_por_100k</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Radiobases por cada 100k habitantes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>lineas_por_1k</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Líneas fijas por cada 1k habitantes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>pib_per_capita</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PIB per capita</t>
-        </is>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
